--- a/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/04 - RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\04 - RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68D5C5D-924F-4FCC-AEBD-207C028BC0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28073558-F98A-4DC6-B567-4294A16E261C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="78">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -197,9 +197,6 @@
     <t>S/I</t>
   </si>
   <si>
-    <t>SIM</t>
-  </si>
-  <si>
     <t>Comprovante de pagamento</t>
   </si>
   <si>
@@ -227,12 +224,6 @@
     <t>THAMIRES E RUDÁ</t>
   </si>
   <si>
-    <t>Aguardando cálculo</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
     <t>NÃO</t>
   </si>
   <si>
@@ -242,38 +233,55 @@
     <t>Respondido</t>
   </si>
   <si>
-    <t>VIGENTE_venc:15/04/2027</t>
-  </si>
-  <si>
-    <t>CATOLÉ DO ROCHA</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 008/2026</t>
-  </si>
-  <si>
-    <t>Enquadramento IP já corrigido</t>
-  </si>
-  <si>
-    <t>1841989-5</t>
-  </si>
-  <si>
-    <t>Arthur</t>
-  </si>
-  <si>
-    <t>Aguardando pagamento</t>
-  </si>
-  <si>
-    <t>Previsão de pagamento: 14/07/2026 (Foi solicitado o comprovante de pagamento no 2º Nível)</t>
+    <t>VIGENTE_venc:14/11/2026</t>
+  </si>
+  <si>
+    <t>SÃO JOÃO DO RIO DO PEIXE</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 012/2025</t>
+  </si>
+  <si>
+    <t>Cobrança Indevida - Perdas nos Reatores</t>
+  </si>
+  <si>
+    <t>381428-2</t>
+  </si>
+  <si>
+    <t>Em análise na ouvidoria da Aneel</t>
+  </si>
+  <si>
+    <t>Débora</t>
+  </si>
+  <si>
+    <t>Reeingressado por conta de pendência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010.585.43825-82 </t>
+  </si>
+  <si>
+    <t>Em análise</t>
+  </si>
+  <si>
+    <t>erro no memorial de cálculo na aplicação do dobro</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Relatório enviado ao parceiro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,6 +369,13 @@
       <color rgb="FF074F69"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -536,10 +551,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -629,38 +645,45 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -982,41 +1005,41 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="34" t="s">
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="37" t="s">
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="39" t="s">
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
@@ -1218,105 +1241,105 @@
       <c r="AR3" s="9"/>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="AV3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="BA3" s="8" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:54" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>64</v>
-      </c>
       <c r="J4" s="21">
-        <v>46087</v>
+        <v>45730</v>
       </c>
       <c r="K4" s="21">
-        <v>46206</v>
-      </c>
-      <c r="L4" s="40">
-        <v>21325.040000000001</v>
+        <v>45798</v>
+      </c>
+      <c r="L4" s="31">
+        <v>251214.62</v>
       </c>
       <c r="M4" s="22">
-        <v>46212</v>
-      </c>
-      <c r="N4" s="40">
-        <v>21325.040000000001</v>
+        <v>45852</v>
+      </c>
+      <c r="N4" s="31">
+        <v>251214.62</v>
       </c>
       <c r="O4" s="23">
         <v>1</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="22">
-        <v>46065</v>
-      </c>
-      <c r="R4" s="25" t="s">
-        <v>52</v>
+        <v>45728</v>
+      </c>
+      <c r="R4" s="25">
+        <v>9569821</v>
       </c>
       <c r="S4" s="22">
-        <v>46087</v>
+        <v>45730</v>
       </c>
       <c r="T4" s="22">
-        <v>46095</v>
+        <v>45758</v>
       </c>
       <c r="U4" s="26" t="s">
         <v>51</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="W4" s="29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Y4" s="22">
-        <v>46161</v>
+        <v>45737</v>
       </c>
       <c r="Z4" s="15" t="s">
         <v>52</v>
@@ -1325,34 +1348,34 @@
         <v>52</v>
       </c>
       <c r="AB4" s="22">
-        <v>46206</v>
+        <v>45749</v>
       </c>
       <c r="AC4" s="22">
-        <v>46191</v>
+        <v>45767</v>
       </c>
       <c r="AD4" s="30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AE4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF4" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" s="22">
+        <v>45897</v>
+      </c>
+      <c r="AI4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="AF4" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG4" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ4" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK4" s="15" t="s">
-        <v>52</v>
+      <c r="AK4" s="22">
+        <v>46240</v>
       </c>
       <c r="AL4" s="15" t="s">
         <v>52</v>
@@ -1373,21 +1396,33 @@
         <v>75</v>
       </c>
       <c r="AR4" s="15" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="AS4" s="15" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="AT4" s="22">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="AU4" s="15"/>
-      <c r="AV4" s="15"/>
-      <c r="AW4" s="15"/>
-      <c r="AX4" s="15"/>
-      <c r="AY4" s="15"/>
-      <c r="AZ4" s="15"/>
-      <c r="BA4" s="15"/>
+      <c r="AV4" s="42">
+        <v>23212.31</v>
+      </c>
+      <c r="AW4" s="22">
+        <v>46120</v>
+      </c>
+      <c r="AX4" s="22">
+        <v>46245</v>
+      </c>
+      <c r="AY4" s="32">
+        <v>2738.5</v>
+      </c>
+      <c r="AZ4" s="22">
+        <v>46184</v>
+      </c>
+      <c r="BA4" s="22">
+        <v>46245</v>
+      </c>
       <c r="BB4" s="1"/>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.3">
